--- a/data/trans_bre/BARTHEL_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/BARTHEL_R2-Habitat-trans_bre.xlsx
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-16,07</t>
+          <t>16,07</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,69</t>
+          <t>8,69</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-11,85</t>
+          <t>11,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-0,16%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-17,63%</t>
+          <t>181,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>-10,17%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-13,72%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 7,53</t>
+          <t>-7,12; 7,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,87; -7,36</t>
+          <t>7,36; 23,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 0,62</t>
+          <t>0,1; 17,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,03; -5,7</t>
+          <t>5,94; 18,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 8,96</t>
+          <t>-50,62; 110,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,26; -8,72</t>
+          <t>53,69; 462,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 0,37</t>
+          <t>0,53; 168,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,08; -6,75</t>
+          <t>34,21; 190,25</t>
         </is>
       </c>
     </row>
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-6,87</t>
+          <t>6,87</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-11,57</t>
+          <t>11,57</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-5,73</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-8,19</t>
+          <t>8,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-7,47%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-14,63%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-6,57%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-9,71%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 0,32</t>
+          <t>-0,95; 13,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,77; -2,71</t>
+          <t>1,09; 21,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 1,96</t>
+          <t>-1,3; 13,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -1,59</t>
+          <t>2,35; 14,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 0,34</t>
+          <t>-11,06; 270,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,9; -3,73</t>
+          <t>2,01; 135,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 2,2</t>
+          <t>-11,21; 147,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,1; -2,05</t>
+          <t>7,95; 110,08</t>
         </is>
       </c>
     </row>
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-8,15</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-13,81</t>
+          <t>13,81</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-14,81</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-8,45%</t>
+          <t>229,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-16,18%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-16,6%</t>
+          <t>136,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>-21,67%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,73; -1,93</t>
+          <t>2,25; 14,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,07; -1,03</t>
+          <t>3,01; 24,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,36; -5,5</t>
+          <t>5,6; 24,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 14,9</t>
+          <t>-13,97; 11,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,98; -2,01</t>
+          <t>14,89; 1166,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,49; -1,62</t>
+          <t>7,6; 314,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,51; -6,5</t>
+          <t>30,16; 361,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 18,25</t>
+          <t>-80,48; 109,9</t>
         </is>
       </c>
     </row>
@@ -912,42 +912,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-6,34</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-5,31</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-11,6</t>
+          <t>11,6</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,59</t>
+          <t>9,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-6,96%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-6,22%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-12,82%</t>
+          <t>121,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-10,89%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 0,2</t>
+          <t>0,72; 13,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 3,31</t>
+          <t>-2,24; 13,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,39; -4,16</t>
+          <t>5,06; 19,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -4,42</t>
+          <t>3,84; 14,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 0,17</t>
+          <t>3,82; 255,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 4,17</t>
+          <t>-12,67; 132,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,05; -4,89</t>
+          <t>40,27; 309,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,0; -5,2</t>
+          <t>23,74; 149,64</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1012,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-5,52</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-10,98</t>
+          <t>10,98</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-9,84</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,17</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-5,99%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-12,9%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>-11,16%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,95%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -2,15</t>
+          <t>1,99; 8,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,71; -5,99</t>
+          <t>6,58; 15,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,35; -5,96</t>
+          <t>5,94; 14,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 3,32</t>
+          <t>-4,58; 10,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -2,31</t>
+          <t>19,54; 144,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,86; -7,36</t>
+          <t>38,02; 131,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -6,9</t>
+          <t>44,23; 150,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 3,89</t>
+          <t>-29,8; 85,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/BARTHEL_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/BARTHEL_R2-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,85</t>
+          <t>12,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>100,99%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 7,42</t>
+          <t>-8,04; 7,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 23,87</t>
+          <t>7,74; 24,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 17,99</t>
+          <t>0,28; 17,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 18,04</t>
+          <t>7,06; 18,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,62; 110,05</t>
+          <t>-56,86; 99,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,69; 462,07</t>
+          <t>52,73; 444,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 168,05</t>
+          <t>-0,7; 162,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,21; 190,25</t>
+          <t>42,04; 199,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,19</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 13,83</t>
+          <t>0,05; 14,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 21,61</t>
+          <t>2,64; 22,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 13,67</t>
+          <t>-2,48; 13,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,39</t>
+          <t>2,5; 14,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 270,74</t>
+          <t>-0,09; 324,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 135,74</t>
+          <t>7,93; 147,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 147,21</t>
+          <t>-17,32; 143,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,95; 110,08</t>
+          <t>13,58; 121,02</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,48</t>
+          <t>9,93</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-21,67%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 14,78</t>
+          <t>2,13; 15,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 24,94</t>
+          <t>0,51; 23,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 24,39</t>
+          <t>4,97; 24,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 11,16</t>
+          <t>2,96; 16,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,89; 1166,67</t>
+          <t>8,8; 1174,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 314,61</t>
+          <t>-2,32; 284,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,16; 361,69</t>
+          <t>29,32; 364,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-80,48; 109,9</t>
+          <t>19,18; 223,9</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,59</t>
+          <t>10,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 13,49</t>
+          <t>-0,53; 12,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 13,35</t>
+          <t>-3,2; 12,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 19,14</t>
+          <t>4,33; 19,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 14,41</t>
+          <t>5,51; 15,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 255,54</t>
+          <t>-10,53; 208,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 132,48</t>
+          <t>-17,66; 130,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,27; 309,42</t>
+          <t>33,43; 292,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,74; 149,64</t>
+          <t>36,86; 175,57</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>10,38</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,99</t>
+          <t>2,41; 9,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 15,74</t>
+          <t>6,34; 15,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 14,47</t>
+          <t>5,36; 13,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 10,68</t>
+          <t>7,29; 13,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,54; 144,47</t>
+          <t>23,43; 143,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,02; 131,05</t>
+          <t>35,77; 131,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,23; 150,4</t>
+          <t>38,08; 131,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 85,63</t>
+          <t>51,57; 120,48</t>
         </is>
       </c>
     </row>
